--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486537_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486537_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9331</v>
+        <v>7.8331</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7498</v>
+        <v>6.5573</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1834</v>
+        <v>1.2759</v>
       </c>
       <c r="G2" t="n">
         <v>1.1946</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0619</v>
+        <v>-0.1619</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.0589</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1955</v>
+        <v>-0.1031</v>
       </c>
       <c r="V2" t="n">
         <v>6.8005</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1798</v>
+        <v>5.5123</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5888</v>
+        <v>3.5514</v>
       </c>
       <c r="F3" t="n">
-        <v>1.591</v>
+        <v>1.9609</v>
       </c>
       <c r="G3" t="n">
         <v>0.5727</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8289</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6489</v>
+        <v>0.3137</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.18</v>
+        <v>0.1899</v>
       </c>
       <c r="V3" t="n">
         <v>3.3485</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6683</v>
+        <v>3.3476</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4518</v>
+        <v>4.4085</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7835</v>
+        <v>-1.061</v>
       </c>
       <c r="G4" t="n">
         <v>3.9165</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0.339</v>
+        <v>0.0183</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3461</v>
+        <v>0.3028</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0071</v>
+        <v>-0.2845</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3698</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7695</v>
+        <v>1.2648</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7129</v>
+        <v>-0.6012</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4824</v>
+        <v>1.8659</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3639</v>
@@ -844,13 +844,13 @@
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2209</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3064</v>
+        <v>-0.1947</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5273</v>
+        <v>0.9109</v>
       </c>
       <c r="V5" t="n">
         <v>1.13</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5972</v>
+        <v>0.6166</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8486</v>
+        <v>0.868</v>
       </c>
       <c r="F6" t="n">
         <v>-0.2514</v>
@@ -922,10 +922,10 @@
         <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9371</v>
+        <v>0.9566</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7557</v>
+        <v>0.7751</v>
       </c>
       <c r="U6" t="n">
         <v>0.1815</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8505</v>
+        <v>0.5249</v>
       </c>
       <c r="E7" t="n">
-        <v>1.228</v>
+        <v>0.4709</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3775</v>
+        <v>0.054</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7084</v>
@@ -1000,13 +1000,13 @@
         <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8188</v>
+        <v>0.4933</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3003</v>
+        <v>0.5432</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4814</v>
+        <v>-0.0499</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5649999999999999</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3308</v>
+        <v>-0.6823</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4955</v>
+        <v>-2.5388</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1647</v>
+        <v>1.8564</v>
       </c>
       <c r="G8" t="n">
         <v>-1.7488</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7655</v>
+        <v>0.414</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1214</v>
+        <v>-0.1646</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8868</v>
+        <v>0.5786</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.583</v>
+        <v>-1.7486</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2756</v>
+        <v>-2.1638</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6926</v>
+        <v>0.4152</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3309</v>
@@ -1156,13 +1156,13 @@
         <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.382</v>
+        <v>-0.5477</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0974</v>
+        <v>-0.18</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9475</v>
+        <v>-1.9167</v>
       </c>
       <c r="E10" t="n">
         <v>-1.7521</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1954</v>
+        <v>-0.1646</v>
       </c>
       <c r="G10" t="n">
         <v>-0.961</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1011</v>
+        <v>0.1319</v>
       </c>
       <c r="T10" t="n">
         <v>0.0805</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8395</v>
+        <v>-2.431</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3577</v>
+        <v>-1.1342</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4818</v>
+        <v>-1.2968</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1271</v>
@@ -1312,13 +1312,13 @@
         <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7347</v>
+        <v>-0.3263</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4795</v>
+        <v>-0.256</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2552</v>
+        <v>-0.0703</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3252</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9396</v>
+        <v>-3.7161</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0882</v>
+        <v>-1.8647</v>
       </c>
       <c r="F12" t="n">
         <v>-1.8514</v>
@@ -1390,10 +1390,10 @@
         <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1801</v>
+        <v>-0.9566</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4795</v>
+        <v>-0.256</v>
       </c>
       <c r="U12" t="n">
         <v>-0.7006</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6517</v>
+        <v>-4.2133</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1905</v>
+        <v>-4.122</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4612</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-1.559</v>
@@ -1468,13 +1468,13 @@
         <v>0.435</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1149</v>
+        <v>-0.6766</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4675</v>
+        <v>-0.399</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6475</v>
+        <v>-0.2776</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3252</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.706299999999999</v>
+        <v>4.391299999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9945000000000004</v>
+        <v>1.679299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7119</v>
+        <v>2.711800000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-1.649799999999999</v>
@@ -1546,13 +1546,13 @@
         <v>9.787599999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1200999999999994</v>
+        <v>0.5646999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3665</v>
+        <v>0.3184</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2462000000000001</v>
+        <v>0.2462999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>6.563800000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARBALLO</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.276</v>
+        <v>3.8154</v>
       </c>
       <c r="E15" t="n">
-        <v>3.982</v>
+        <v>2.2961</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.706</v>
+        <v>1.5193</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6307</v>
+        <v>2.2628</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1017</v>
+        <v>0.1065</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.471</v>
+        <v>2.1563</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4395</v>
+        <v>1.7075</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5726</v>
+        <v>0.0428</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1331</v>
+        <v>1.6647</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1912</v>
+        <v>0.5553</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5291</v>
+        <v>0.0636</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3379</v>
+        <v>0.4916</v>
       </c>
       <c r="P15" t="n">
-        <v>0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1149</v>
+        <v>0.4449</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.3509</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.442</v>
+        <v>0.094</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8902</v>
+        <v>1.3252</v>
       </c>
       <c r="W15" t="n">
-        <v>3.2154</v>
+        <v>1.3252</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>M. FERNANDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1153</v>
+        <v>3.7474</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9608</v>
+        <v>4.0937</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1546</v>
+        <v>-0.3463</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2628</v>
+        <v>1.6307</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1065</v>
+        <v>2.1017</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1563</v>
+        <v>-0.471</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7075</v>
+        <v>1.4395</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0428</v>
+        <v>1.5726</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6647</v>
+        <v>-0.1331</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5553</v>
+        <v>0.1912</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0636</v>
+        <v>0.5291</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4916</v>
+        <v>-0.3379</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2551</v>
+        <v>-0.6435</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0156</v>
+        <v>-0.5612</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2708</v>
+        <v>-0.0823</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3252</v>
+        <v>1.8902</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3252</v>
+        <v>3.2154</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>D. SARAIVA SEIXAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7275</v>
+        <v>0.9105</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7452</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0177</v>
+        <v>0.1087</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0518</v>
+        <v>1.657</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5482</v>
+        <v>0.888</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5036</v>
+        <v>0.769</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6486</v>
+        <v>1.1822</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5721000000000001</v>
+        <v>1.3719</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0765</v>
+        <v>-0.1896</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4032</v>
+        <v>0.4748</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9761</v>
+        <v>-0.4838</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4271</v>
+        <v>0.9586</v>
       </c>
       <c r="P17" t="n">
-        <v>0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1956</v>
+        <v>1.3612</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8362</v>
+        <v>0.5119</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3594</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.3899</v>
+        <v>-1.8902</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.6504</v>
+        <v>-2.0854</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SARAIVA SEIXAS</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6935</v>
+        <v>0.5933</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9136</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2202</v>
+        <v>-0.1461</v>
       </c>
       <c r="G18" t="n">
-        <v>1.657</v>
+        <v>2.0518</v>
       </c>
       <c r="H18" t="n">
-        <v>0.888</v>
+        <v>1.5482</v>
       </c>
       <c r="I18" t="n">
-        <v>0.769</v>
+        <v>0.5036</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1822</v>
+        <v>0.6486</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3719</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1896</v>
+        <v>0.0765</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4748</v>
+        <v>1.4032</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4838</v>
+        <v>0.9761</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9586</v>
+        <v>0.4271</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1441</v>
+        <v>1.0614</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6237</v>
+        <v>0.8304</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5204</v>
+        <v>0.231</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8902</v>
+        <v>-3.3899</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.0854</v>
+        <v>-2.6504</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.633</v>
+        <v>0.5041</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2368</v>
+        <v>0.0512</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6038</v>
+        <v>0.4529</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1787</v>
+        <v>0.4215</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.742</v>
+        <v>0.8303</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4367</v>
+        <v>-0.4088</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5938</v>
+        <v>-0.1411</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7086</v>
+        <v>0.5657</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1147</v>
+        <v>-0.7068</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5849</v>
+        <v>0.5626</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0335</v>
+        <v>0.2645</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5514</v>
+        <v>0.298</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4642</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7006</v>
+        <v>0.1923</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2364</v>
+        <v>-0.1097</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4848</v>
+        <v>0.3902</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0606</v>
+        <v>0.9015</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5454</v>
+        <v>-0.5113</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4215</v>
+        <v>-1.1787</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8303</v>
+        <v>-0.742</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4088</v>
+        <v>-0.4367</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1411</v>
+        <v>-0.5938</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5657</v>
+        <v>-0.7086</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7068</v>
+        <v>0.1147</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5626</v>
+        <v>-0.5849</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2645</v>
+        <v>-0.0335</v>
       </c>
       <c r="O20" t="n">
-        <v>0.298</v>
+        <v>-0.5514</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0633</v>
+        <v>0.2214</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0805</v>
+        <v>0.3653</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0172</v>
+        <v>-0.1439</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0285</v>
+        <v>0.2033</v>
       </c>
       <c r="E21" t="n">
         <v>0.1962</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1677</v>
+        <v>0.007</v>
       </c>
       <c r="G21" t="n">
         <v>0.2952</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3408</v>
+        <v>0.5155</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2704</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6112</v>
+        <v>0.7859</v>
       </c>
       <c r="V21" t="n">
         <v>-1.695</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6082</v>
+        <v>-0.7058</v>
       </c>
       <c r="E22" t="n">
         <v>-1.526</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9177</v>
+        <v>0.8202</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1098</v>
@@ -2170,13 +2170,13 @@
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.716</v>
+        <v>-0.8136</v>
       </c>
       <c r="T22" t="n">
         <v>-0.6044</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1115</v>
+        <v>-0.2091</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7163</v>
+        <v>-1.2098</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3404</v>
+        <v>-0.2988</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3759</v>
+        <v>-0.9109</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0848</v>
+        <v>0.8871</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3629</v>
+        <v>2.8163</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2781</v>
+        <v>-1.9292</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4655</v>
+        <v>1.3773</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4655</v>
+        <v>3.2666</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.8893</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6193</v>
+        <v>-0.4902</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8974</v>
+        <v>-0.4504</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2781</v>
+        <v>-0.0399</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.435</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5431</v>
+        <v>0.2283</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2572</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2859</v>
+        <v>0.2944</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1745</v>
+        <v>-1.8902</v>
       </c>
       <c r="W23" t="n">
-        <v>0.9554</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.13</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7859</v>
+        <v>-2.1197</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3047</v>
+        <v>-2.011</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4813</v>
+        <v>-0.1087</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8871</v>
+        <v>-2.0848</v>
       </c>
       <c r="H24" t="n">
-        <v>2.8163</v>
+        <v>-2.3629</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.9292</v>
+        <v>0.2781</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3773</v>
+        <v>-1.4655</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2666</v>
+        <v>-1.4655</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.8893</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4902</v>
+        <v>-0.6193</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4504</v>
+        <v>-0.8974</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0399</v>
+        <v>0.2781</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3478</v>
+        <v>0.1397</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0719</v>
+        <v>-0.4134</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2759</v>
+        <v>0.5531</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.8902</v>
+        <v>-0.1745</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.9554</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4552</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8223</v>
+        <v>-2.1402</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2231</v>
+        <v>-1.6643</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5992</v>
+        <v>-0.4759</v>
       </c>
       <c r="G25" t="n">
         <v>-0.8100000000000001</v>
@@ -2404,13 +2404,13 @@
         <v>0.2175</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0548</v>
+        <v>0.6273</v>
       </c>
       <c r="T25" t="n">
-        <v>0.012</v>
+        <v>0.5708</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0668</v>
+        <v>0.0565</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.7322</v>
+        <v>-5.3481</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.2917</v>
+        <v>-6.1799</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5595</v>
+        <v>0.8318</v>
       </c>
       <c r="G26" t="n">
         <v>-3.3729</v>
@@ -2482,13 +2482,13 @@
         <v>1.7401</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1423</v>
+        <v>-0.7583</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.1524</v>
+        <v>-1.0407</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0101</v>
+        <v>0.2824</v>
       </c>
       <c r="V26" t="n">
         <v>-1.8695</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.706299999999999</v>
+        <v>-1.3594</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.711899999999999</v>
+        <v>-2.600000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.9946</v>
+        <v>1.2407</v>
       </c>
       <c r="G27" t="n">
         <v>1.6499</v>
@@ -2542,10 +2542,10 @@
         <v>-3.8487</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9951000000000005</v>
+        <v>0.9951000000000003</v>
       </c>
       <c r="N27" t="n">
-        <v>0.2260999999999999</v>
+        <v>0.2261000000000001</v>
       </c>
       <c r="O27" t="n">
         <v>0.7685999999999997</v>
@@ -2560,19 +2560,19 @@
         <v>10.8752</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1201999999999996</v>
+        <v>2.4669</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2462000000000002</v>
+        <v>-0.1345999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3663999999999998</v>
+        <v>2.6016</v>
       </c>
       <c r="V27" t="n">
         <v>-6.5639</v>
       </c>
       <c r="W27" t="n">
-        <v>6.667400000000001</v>
+        <v>6.667399999999999</v>
       </c>
       <c r="X27" t="n">
         <v>-13.2314</v>
